--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.32459429511508</v>
+        <v>4.115246572956201</v>
       </c>
       <c r="D2" t="n">
-        <v>56.153395570971</v>
+        <v>9.124926780282788</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F2" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.51599783699777</v>
+        <v>4.308849648512139</v>
       </c>
       <c r="D3" t="n">
-        <v>50.51598339676391</v>
+        <v>8.208847301974137</v>
       </c>
       <c r="E3" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F3" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.11136147043059</v>
+        <v>6.680596238944971</v>
       </c>
       <c r="D4" t="n">
-        <v>49.09779857066129</v>
+        <v>7.97839226773246</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F4" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.59363384891968</v>
+        <v>2.208965500449449</v>
       </c>
       <c r="D5" t="n">
-        <v>40.90439125063246</v>
+        <v>6.646963578227775</v>
       </c>
       <c r="E5" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F5" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.18825675780526</v>
+        <v>7.018091723143354</v>
       </c>
       <c r="D6" t="n">
-        <v>51.14999885392803</v>
+        <v>8.311874813763305</v>
       </c>
       <c r="E6" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F6" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.183517910538306</v>
+        <v>1.492321660462475</v>
       </c>
       <c r="D7" t="n">
-        <v>44.3258230686521</v>
+        <v>7.202946248655966</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F7" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>57.91626809339355</v>
+        <v>9.411393565176454</v>
       </c>
       <c r="D8" t="n">
-        <v>49.25222641762769</v>
+        <v>8.0034867928645</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F8" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.50438027449517</v>
+        <v>4.306961794605466</v>
       </c>
       <c r="D9" t="n">
-        <v>43.93797534130146</v>
+        <v>7.139920992961487</v>
       </c>
       <c r="E9" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F9" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.46287660585473</v>
+        <v>6.412717448451394</v>
       </c>
       <c r="D10" t="n">
-        <v>19.87219459510729</v>
+        <v>3.229231621704935</v>
       </c>
       <c r="E10" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F10" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.57145140281005</v>
+        <v>3.505360852956633</v>
       </c>
       <c r="D11" t="n">
-        <v>23.07881295911848</v>
+        <v>3.750307105856753</v>
       </c>
       <c r="E11" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F11" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.98032819403684</v>
+        <v>5.521803331530986</v>
       </c>
       <c r="D12" t="n">
-        <v>17.45426888378811</v>
+        <v>2.836318693615568</v>
       </c>
       <c r="E12" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F12" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.55186814202175</v>
+        <v>5.127178573078534</v>
       </c>
       <c r="D13" t="n">
-        <v>6.311325274395197</v>
+        <v>1.02559035708922</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F13" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.92025344359826</v>
+        <v>4.212041184584717</v>
       </c>
       <c r="D14" t="n">
-        <v>24.48120199750502</v>
+        <v>3.978195324594565</v>
       </c>
       <c r="E14" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F14" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.40739769000065</v>
+        <v>7.053702124625106</v>
       </c>
       <c r="D15" t="n">
-        <v>43.3702728071477</v>
+        <v>7.047669331161502</v>
       </c>
       <c r="E15" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F15" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>11.20835756706844</v>
+        <v>1.821358104648621</v>
       </c>
       <c r="D16" t="n">
-        <v>12.62537781531885</v>
+        <v>2.051623894989313</v>
       </c>
       <c r="E16" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F16" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.24666668434686</v>
+        <v>4.752583336206365</v>
       </c>
       <c r="D17" t="n">
-        <v>21.95605085014699</v>
+        <v>3.567858263148886</v>
       </c>
       <c r="E17" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F17" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.65048460374642</v>
+        <v>3.680703748108794</v>
       </c>
       <c r="D18" t="n">
-        <v>22.1131666609579</v>
+        <v>3.593389582405659</v>
       </c>
       <c r="E18" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F18" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.26811851473791</v>
+        <v>3.45606925864491</v>
       </c>
       <c r="D19" t="n">
-        <v>17.79496323762005</v>
+        <v>2.891681526113258</v>
       </c>
       <c r="E19" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F19" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>17.71871627098178</v>
+        <v>2.87929139403454</v>
       </c>
       <c r="D20" t="n">
-        <v>16.26483753316796</v>
+        <v>2.643036099139793</v>
       </c>
       <c r="E20" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F20" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>43.46867111676116</v>
+        <v>7.063659056473688</v>
       </c>
       <c r="D21" t="n">
-        <v>42.47225147379464</v>
+        <v>6.901740864491629</v>
       </c>
       <c r="E21" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F21" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>13.74762610348994</v>
+        <v>2.233989241817116</v>
       </c>
       <c r="D22" t="n">
-        <v>13.57733886691695</v>
+        <v>2.206317565874004</v>
       </c>
       <c r="E22" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F22" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>8.991753157656039</v>
+        <v>1.461159888119106</v>
       </c>
       <c r="D23" t="n">
-        <v>8.152252307145543</v>
+        <v>1.324740999911151</v>
       </c>
       <c r="E23" t="n">
-        <v>12.7870845404415</v>
+        <v>2.077901237821744</v>
       </c>
       <c r="F23" t="n">
-        <v>15.87335834852495</v>
+        <v>2.579420731635305</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
